--- a/Vulnerability Test Results/test-cases.xlsx
+++ b/Vulnerability Test Results/test-cases.xlsx
@@ -2940,8 +2940,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="75" customWidth="1" min="3" max="3"/>
-    <col width="91" customWidth="1" min="4" max="4"/>
+    <col width="71" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
     <col width="103" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="51" customWidth="1" min="7" max="7"/>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Verify patient login with valid credentials (Variant #1)</t>
+          <t>Verify patient login with valid credentials</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Verify login with invalid password (Variant #2)</t>
+          <t>Verify login with invalid password - Step 2</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Verify login with non-existent email (Variant #3)</t>
+          <t>Verify login with non-existent email - Step 3</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Verify registration with missing email (Variant #4)</t>
+          <t>Verify registration with missing email - Step 4</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT token format and algorithm (Variant #5)</t>
+          <t>Verify JWT token format and algorithm - Step 5</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Verify token expiration claim (exp) (Variant #6)</t>
+          <t>Verify token expiration claim (exp) - Step 6</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Verify login rate limiting (Variant #7)</t>
+          <t>Verify login rate limiting - Step 7</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Verify password storage security (Variant #8)</t>
+          <t>Verify password storage security - Step 8</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Verify patient login with valid credentials (Variant #9)</t>
+          <t>Verify patient login with valid credentials - Step 9</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Verify login with invalid password (Variant #10)</t>
+          <t>Verify login with invalid password - Step 10</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Verify login with non-existent email (Variant #11)</t>
+          <t>Verify login with non-existent email - Step 11</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Verify registration with missing email (Variant #12)</t>
+          <t>Verify registration with missing email - Step 12</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT token format and algorithm (Variant #13)</t>
+          <t>Verify JWT token format and algorithm - Step 13</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Verify token expiration claim (exp) (Variant #14)</t>
+          <t>Verify token expiration claim (exp) - Step 14</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Verify login rate limiting (Variant #15)</t>
+          <t>Verify login rate limiting - Step 15</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Verify password storage security (Variant #16)</t>
+          <t>Verify password storage security - Step 16</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Verify patient login with valid credentials (Variant #17)</t>
+          <t>Verify patient login with valid credentials - Step 17</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Verify login with invalid password (Variant #18)</t>
+          <t>Verify login with invalid password - Step 18</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Verify login with non-existent email (Variant #19)</t>
+          <t>Verify login with non-existent email - Step 19</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Verify registration with missing email (Variant #20)</t>
+          <t>Verify registration with missing email - Step 20</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT token format and algorithm (Variant #21)</t>
+          <t>Verify JWT token format and algorithm - Step 21</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Verify token expiration claim (exp) (Variant #22)</t>
+          <t>Verify token expiration claim (exp) - Step 22</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Verify login rate limiting (Variant #23)</t>
+          <t>Verify login rate limiting - Step 23</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Verify password storage security (Variant #24)</t>
+          <t>Verify password storage security - Step 24</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Verify patient login with valid credentials (Variant #25)</t>
+          <t>Verify patient login with valid credentials - Step 25</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Verify login with invalid password (Variant #26)</t>
+          <t>Verify login with invalid password - Step 26</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Verify login with non-existent email (Variant #27)</t>
+          <t>Verify login with non-existent email - Step 27</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Verify registration with missing email (Variant #28)</t>
+          <t>Verify registration with missing email - Step 28</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT token format and algorithm (Variant #29)</t>
+          <t>Verify JWT token format and algorithm - Step 29</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Verify token expiration claim (exp) (Variant #30)</t>
+          <t>Verify token expiration claim (exp) - Step 30</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Verify login rate limiting (Variant #31)</t>
+          <t>Verify login rate limiting - Step 31</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Verify password storage security (Variant #32)</t>
+          <t>Verify password storage security - Step 32</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Verify patient login with valid credentials (Variant #33)</t>
+          <t>Verify patient login with valid credentials - Step 33</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Verify login with invalid password (Variant #34)</t>
+          <t>Verify login with invalid password - Step 34</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Verify login with non-existent email (Variant #35)</t>
+          <t>Verify login with non-existent email - Step 35</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authentication Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Authentication Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #1)</t>
+          <t>Verify customer access to order creation</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #2)</t>
+          <t>Verify customer blocked from adding medicines - Step 2</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #3)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 3</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on order details query (Variant #4)</t>
+          <t>Verify IDOR on order details query - Step 4</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on prescription query (Variant #5)</t>
+          <t>Verify IDOR on prescription query - Step 5</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Verify unauthenticated access to admin stats (Variant #6)</t>
+          <t>Verify unauthenticated access to admin stats - Step 6</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Verify order status update role guard (Variant #7)</t>
+          <t>Verify order status update role guard - Step 7</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #8)</t>
+          <t>Verify customer access to order creation - Step 8</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #9)</t>
+          <t>Verify customer blocked from adding medicines - Step 9</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #10)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 10</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on order details query (Variant #11)</t>
+          <t>Verify IDOR on order details query - Step 11</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on prescription query (Variant #12)</t>
+          <t>Verify IDOR on prescription query - Step 12</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Verify unauthenticated access to admin stats (Variant #13)</t>
+          <t>Verify unauthenticated access to admin stats - Step 13</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Verify order status update role guard (Variant #14)</t>
+          <t>Verify order status update role guard - Step 14</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #15)</t>
+          <t>Verify customer access to order creation - Step 15</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #16)</t>
+          <t>Verify customer blocked from adding medicines - Step 16</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #17)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 17</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on order details query (Variant #18)</t>
+          <t>Verify IDOR on order details query - Step 18</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on prescription query (Variant #19)</t>
+          <t>Verify IDOR on prescription query - Step 19</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Verify unauthenticated access to admin stats (Variant #20)</t>
+          <t>Verify unauthenticated access to admin stats - Step 20</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Verify order status update role guard (Variant #21)</t>
+          <t>Verify order status update role guard - Step 21</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #22)</t>
+          <t>Verify customer access to order creation - Step 22</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #23)</t>
+          <t>Verify customer blocked from adding medicines - Step 23</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #24)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 24</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on order details query (Variant #25)</t>
+          <t>Verify IDOR on order details query - Step 25</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on prescription query (Variant #26)</t>
+          <t>Verify IDOR on prescription query - Step 26</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Verify unauthenticated access to admin stats (Variant #27)</t>
+          <t>Verify unauthenticated access to admin stats - Step 27</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Verify order status update role guard (Variant #28)</t>
+          <t>Verify order status update role guard - Step 28</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #29)</t>
+          <t>Verify customer access to order creation - Step 29</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #30)</t>
+          <t>Verify customer blocked from adding medicines - Step 30</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #31)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 31</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on order details query (Variant #32)</t>
+          <t>Verify IDOR on order details query - Step 32</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on prescription query (Variant #33)</t>
+          <t>Verify IDOR on prescription query - Step 33</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Verify unauthenticated access to admin stats (Variant #34)</t>
+          <t>Verify unauthenticated access to admin stats - Step 34</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Verify order status update role guard (Variant #35)</t>
+          <t>Verify order status update role guard - Step 35</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #36)</t>
+          <t>Verify customer access to order creation - Step 36</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #36</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 36</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #37)</t>
+          <t>Verify customer blocked from adding medicines - Step 37</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #37</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 37</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #38)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 38</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #38</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 38</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on order details query (Variant #39)</t>
+          <t>Verify IDOR on order details query - Step 39</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #39</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 39</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Verify IDOR on prescription query (Variant #40)</t>
+          <t>Verify IDOR on prescription query - Step 40</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #40</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 40</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Verify unauthenticated access to admin stats (Variant #41)</t>
+          <t>Verify unauthenticated access to admin stats - Step 41</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #41</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 41</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Verify order status update role guard (Variant #42)</t>
+          <t>Verify order status update role guard - Step 42</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #42</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 42</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Verify customer access to order creation (Variant #43)</t>
+          <t>Verify customer access to order creation - Step 43</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #43</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 43</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Verify customer blocked from adding medicines (Variant #44)</t>
+          <t>Verify customer blocked from adding medicines - Step 44</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #44</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 44</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Verify pharmacist access to medicine catalog add (Variant #45)</t>
+          <t>Verify pharmacist access to medicine catalog add - Step 45</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Authorization Tests - Sub-scenario #45</t>
+          <t>Validate backend security contract for Authorization Tests - Sub-scenario 45</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -7352,12 +7352,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #1)</t>
+          <t>Verify register with empty body payload</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #2)</t>
+          <t>Verify order creation with empty cart items array - Step 2</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #3)</t>
+          <t>Verify medicine creation with negative price - Step 3</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #4)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 4</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #5)</t>
+          <t>Verify invalid email format during registration - Step 5</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #6)</t>
+          <t>Verify register with empty body payload - Step 6</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #7)</t>
+          <t>Verify order creation with empty cart items array - Step 7</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #8)</t>
+          <t>Verify medicine creation with negative price - Step 8</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #9)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 9</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #10)</t>
+          <t>Verify invalid email format during registration - Step 10</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #11)</t>
+          <t>Verify register with empty body payload - Step 11</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #12)</t>
+          <t>Verify order creation with empty cart items array - Step 12</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #13)</t>
+          <t>Verify medicine creation with negative price - Step 13</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -8054,12 +8054,12 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #14)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 14</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #15)</t>
+          <t>Verify invalid email format during registration - Step 15</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #16)</t>
+          <t>Verify register with empty body payload - Step 16</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #17)</t>
+          <t>Verify order creation with empty cart items array - Step 17</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #18)</t>
+          <t>Verify medicine creation with negative price - Step 18</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #19)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 19</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #20)</t>
+          <t>Verify invalid email format during registration - Step 20</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #21)</t>
+          <t>Verify register with empty body payload - Step 21</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #22)</t>
+          <t>Verify order creation with empty cart items array - Step 22</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #23)</t>
+          <t>Verify medicine creation with negative price - Step 23</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #24)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 24</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #25)</t>
+          <t>Verify invalid email format during registration - Step 25</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #26)</t>
+          <t>Verify register with empty body payload - Step 26</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #27)</t>
+          <t>Verify order creation with empty cart items array - Step 27</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #28)</t>
+          <t>Verify medicine creation with negative price - Step 28</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #29)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 29</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #30)</t>
+          <t>Verify invalid email format during registration - Step 30</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #31)</t>
+          <t>Verify register with empty body payload - Step 31</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #32)</t>
+          <t>Verify order creation with empty cart items array - Step 32</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #33)</t>
+          <t>Verify medicine creation with negative price - Step 33</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #34)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 34</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #35)</t>
+          <t>Verify invalid email format during registration - Step 35</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #36)</t>
+          <t>Verify register with empty body payload - Step 36</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #36</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 36</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #37)</t>
+          <t>Verify order creation with empty cart items array - Step 37</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #37</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 37</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #38)</t>
+          <t>Verify medicine creation with negative price - Step 38</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #38</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 38</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #39)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 39</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #39</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 39</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #40)</t>
+          <t>Verify invalid email format during registration - Step 40</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #40</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 40</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Verify register with empty body payload (Variant #41)</t>
+          <t>Verify register with empty body payload - Step 41</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #41</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 41</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Verify order creation with empty cart items array (Variant #42)</t>
+          <t>Verify order creation with empty cart items array - Step 42</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #42</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 42</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Verify medicine creation with negative price (Variant #43)</t>
+          <t>Verify medicine creation with negative price - Step 43</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #43</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 43</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Verify oversized payload attack (&gt;10MB) (Variant #44)</t>
+          <t>Verify oversized payload attack (&gt;10MB) - Step 44</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #44</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 44</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Verify invalid email format during registration (Variant #45)</t>
+          <t>Verify invalid email format during registration - Step 45</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Input Validation Tests - Sub-scenario #45</t>
+          <t>Validate backend security contract for Input Validation Tests - Sub-scenario 45</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #1)</t>
+          <t>Verify SQL injection in login email field</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #2)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 2</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #3)</t>
+          <t>Verify Command Injection in search parameter - Step 3</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -9944,12 +9944,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #4)</t>
+          <t>Verify Path Traversal in static file request - Step 4</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #5)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 5</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #6)</t>
+          <t>Verify SQL injection in login email field - Step 6</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #7)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 7</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #8)</t>
+          <t>Verify Command Injection in search parameter - Step 8</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #9)</t>
+          <t>Verify Path Traversal in static file request - Step 9</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -10268,12 +10268,12 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #10)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 10</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #11)</t>
+          <t>Verify SQL injection in login email field - Step 11</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #12)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 12</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -10430,12 +10430,12 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #13)</t>
+          <t>Verify Command Injection in search parameter - Step 13</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #14)</t>
+          <t>Verify Path Traversal in static file request - Step 14</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #15)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 15</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #16)</t>
+          <t>Verify SQL injection in login email field - Step 16</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #17)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 17</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #18)</t>
+          <t>Verify Command Injection in search parameter - Step 18</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #19)</t>
+          <t>Verify Path Traversal in static file request - Step 19</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #20)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 20</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #21)</t>
+          <t>Verify SQL injection in login email field - Step 21</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -10916,12 +10916,12 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #22)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 22</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #23)</t>
+          <t>Verify Command Injection in search parameter - Step 23</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #24)</t>
+          <t>Verify Path Traversal in static file request - Step 24</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -11078,12 +11078,12 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #25)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 25</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #26)</t>
+          <t>Verify SQL injection in login email field - Step 26</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #27)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 27</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #28)</t>
+          <t>Verify Command Injection in search parameter - Step 28</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #29)</t>
+          <t>Verify Path Traversal in static file request - Step 29</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #30)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 30</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #31)</t>
+          <t>Verify SQL injection in login email field - Step 31</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #32)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 32</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #33)</t>
+          <t>Verify Command Injection in search parameter - Step 33</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -11564,12 +11564,12 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #34)</t>
+          <t>Verify Path Traversal in static file request - Step 34</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #35)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 35</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #36)</t>
+          <t>Verify SQL injection in login email field - Step 36</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #36</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 36</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #37)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 37</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #37</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 37</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #38)</t>
+          <t>Verify Command Injection in search parameter - Step 38</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #38</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 38</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #39)</t>
+          <t>Verify Path Traversal in static file request - Step 39</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #39</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 39</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #40)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 40</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #40</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 40</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #41)</t>
+          <t>Verify SQL injection in login email field - Step 41</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #41</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 41</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #42)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 42</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #42</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 42</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #43)</t>
+          <t>Verify Command Injection in search parameter - Step 43</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #43</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 43</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #44)</t>
+          <t>Verify Path Traversal in static file request - Step 44</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #44</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 44</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #45)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 45</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #45</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 45</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -12212,12 +12212,12 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #46)</t>
+          <t>Verify SQL injection in login email field - Step 46</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #46</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 46</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #47)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 47</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #47</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 47</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -12320,12 +12320,12 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #48)</t>
+          <t>Verify Command Injection in search parameter - Step 48</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #48</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 48</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #49)</t>
+          <t>Verify Path Traversal in static file request - Step 49</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #49</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 49</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -12428,12 +12428,12 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #50)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 50</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #50</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 50</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -12482,12 +12482,12 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #51)</t>
+          <t>Verify SQL injection in login email field - Step 51</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #51</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 51</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #52)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 52</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #52</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 52</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -12590,12 +12590,12 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #53)</t>
+          <t>Verify Command Injection in search parameter - Step 53</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #53</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 53</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -12644,12 +12644,12 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #54)</t>
+          <t>Verify Path Traversal in static file request - Step 54</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #54</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 54</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -12698,12 +12698,12 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #55)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 55</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #55</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 55</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #56)</t>
+          <t>Verify SQL injection in login email field - Step 56</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #56</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 56</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #57)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 57</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #57</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 57</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #58)</t>
+          <t>Verify Command Injection in search parameter - Step 58</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #58</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 58</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -12914,12 +12914,12 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #59)</t>
+          <t>Verify Path Traversal in static file request - Step 59</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #59</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 59</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #60)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 60</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #60</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 60</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -13022,12 +13022,12 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Verify SQL injection in login email field (Variant #61)</t>
+          <t>Verify SQL injection in login email field - Step 61</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #61</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 61</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Verify NoSQL injection operator in auth body (Variant #62)</t>
+          <t>Verify NoSQL injection operator in auth body - Step 62</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #62</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 62</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Verify Command Injection in search parameter (Variant #63)</t>
+          <t>Verify Command Injection in search parameter - Step 63</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #63</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 63</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Verify Path Traversal in static file request (Variant #64)</t>
+          <t>Verify Path Traversal in static file request - Step 64</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #64</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 64</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Verify Cross-Site Scripting (XSS) in user name (Variant #65)</t>
+          <t>Verify Cross-Site Scripting (XSS) in user name - Step 65</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Injection Tests - Sub-scenario #65</t>
+          <t>Validate backend security contract for Injection Tests - Sub-scenario 65</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -13292,12 +13292,12 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #1)</t>
+          <t>Verify JWT signature validation with tampered payload</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -13346,12 +13346,12 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #2)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 2</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -13400,12 +13400,12 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #3)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 3</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #4)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 4</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #5)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 5</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #6)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 6</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #7)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 7</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #8)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 8</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #9)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 9</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #10)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 10</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #11)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 11</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #12)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 12</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
@@ -13940,12 +13940,12 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #13)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 13</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #14)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 14</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -14048,12 +14048,12 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #15)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 15</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -14102,12 +14102,12 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #16)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 16</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
@@ -14156,12 +14156,12 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #17)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 17</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
@@ -14210,12 +14210,12 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #18)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 18</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #19)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 19</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #20)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 20</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #21)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 21</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -14426,12 +14426,12 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #22)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 22</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
@@ -14480,12 +14480,12 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Verify hardcoded JWT secret vulnerability (Variant #23)</t>
+          <t>Verify hardcoded JWT secret vulnerability - Step 23</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
@@ -14534,12 +14534,12 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Verify HTTPS SSL/TLS enforced (Variant #24)</t>
+          <t>Verify HTTPS SSL/TLS enforced - Step 24</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
@@ -14588,12 +14588,12 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Verify JWT signature validation with tampered payload (Variant #25)</t>
+          <t>Verify JWT signature validation with tampered payload - Step 25</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Cryptography Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Cryptography Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -14642,12 +14642,12 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #1)</t>
+          <t>Verify delivery partner OTP excluded from order response</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #2)</t>
+          <t>Verify password excluded from user profile JSON - Step 2</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #3)</t>
+          <t>Verify API error responses do not leak stack traces - Step 3</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
@@ -14804,12 +14804,12 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #4)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 4</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -14858,12 +14858,12 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #5)</t>
+          <t>Verify password excluded from user profile JSON - Step 5</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
@@ -14912,12 +14912,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #6)</t>
+          <t>Verify API error responses do not leak stack traces - Step 6</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -14966,12 +14966,12 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #7)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 7</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
@@ -15020,12 +15020,12 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #8)</t>
+          <t>Verify password excluded from user profile JSON - Step 8</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -15074,12 +15074,12 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #9)</t>
+          <t>Verify API error responses do not leak stack traces - Step 9</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
@@ -15128,12 +15128,12 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #10)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 10</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -15182,12 +15182,12 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #11)</t>
+          <t>Verify password excluded from user profile JSON - Step 11</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #12)</t>
+          <t>Verify API error responses do not leak stack traces - Step 12</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -15290,12 +15290,12 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #13)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 13</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
@@ -15344,12 +15344,12 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #14)</t>
+          <t>Verify password excluded from user profile JSON - Step 14</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -15398,12 +15398,12 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #15)</t>
+          <t>Verify API error responses do not leak stack traces - Step 15</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
@@ -15452,12 +15452,12 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #16)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 16</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -15506,12 +15506,12 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #17)</t>
+          <t>Verify password excluded from user profile JSON - Step 17</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #18)</t>
+          <t>Verify API error responses do not leak stack traces - Step 18</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -15614,12 +15614,12 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #19)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 19</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
@@ -15668,12 +15668,12 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #20)</t>
+          <t>Verify password excluded from user profile JSON - Step 20</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #21)</t>
+          <t>Verify API error responses do not leak stack traces - Step 21</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
@@ -15776,12 +15776,12 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #22)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 22</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -15830,12 +15830,12 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #23)</t>
+          <t>Verify password excluded from user profile JSON - Step 23</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
@@ -15884,12 +15884,12 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #24)</t>
+          <t>Verify API error responses do not leak stack traces - Step 24</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -15938,12 +15938,12 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #25)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 25</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
@@ -15992,12 +15992,12 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #26)</t>
+          <t>Verify password excluded from user profile JSON - Step 26</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -16046,12 +16046,12 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #27)</t>
+          <t>Verify API error responses do not leak stack traces - Step 27</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -16100,12 +16100,12 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #28)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 28</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -16154,12 +16154,12 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #29)</t>
+          <t>Verify password excluded from user profile JSON - Step 29</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -16208,12 +16208,12 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #30)</t>
+          <t>Verify API error responses do not leak stack traces - Step 30</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -16262,12 +16262,12 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #31)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 31</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -16316,12 +16316,12 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #32)</t>
+          <t>Verify password excluded from user profile JSON - Step 32</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -16370,12 +16370,12 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Verify API error responses do not leak stack traces (Variant #33)</t>
+          <t>Verify API error responses do not leak stack traces - Step 33</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -16424,12 +16424,12 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Verify delivery partner OTP excluded from order response (Variant #34)</t>
+          <t>Verify delivery partner OTP excluded from order response - Step 34</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -16478,12 +16478,12 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Verify password excluded from user profile JSON (Variant #35)</t>
+          <t>Verify password excluded from user profile JSON - Step 35</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Sensitive Data Exposure Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -16532,12 +16532,12 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #1)</t>
+          <t>Verify total order price calculation math</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #2)</t>
+          <t>Verify free delivery threshold ($200+) - Step 2</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
@@ -16640,12 +16640,12 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #3)</t>
+          <t>Verify prescription status state machine - Step 3</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -16694,12 +16694,12 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #4)</t>
+          <t>Verify total order price calculation math - Step 4</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
@@ -16748,12 +16748,12 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #5)</t>
+          <t>Verify free delivery threshold ($200+) - Step 5</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #6)</t>
+          <t>Verify prescription status state machine - Step 6</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -16856,12 +16856,12 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #7)</t>
+          <t>Verify total order price calculation math - Step 7</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -16910,12 +16910,12 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #8)</t>
+          <t>Verify free delivery threshold ($200+) - Step 8</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
@@ -16964,12 +16964,12 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #9)</t>
+          <t>Verify prescription status state machine - Step 9</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #10)</t>
+          <t>Verify total order price calculation math - Step 10</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr">
@@ -17072,12 +17072,12 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #11)</t>
+          <t>Verify free delivery threshold ($200+) - Step 11</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #12)</t>
+          <t>Verify prescription status state machine - Step 12</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #13)</t>
+          <t>Verify total order price calculation math - Step 13</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -17234,12 +17234,12 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #14)</t>
+          <t>Verify free delivery threshold ($200+) - Step 14</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
@@ -17288,12 +17288,12 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #15)</t>
+          <t>Verify prescription status state machine - Step 15</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -17342,12 +17342,12 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #16)</t>
+          <t>Verify total order price calculation math - Step 16</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
@@ -17396,12 +17396,12 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #17)</t>
+          <t>Verify free delivery threshold ($200+) - Step 17</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -17450,12 +17450,12 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #18)</t>
+          <t>Verify prescription status state machine - Step 18</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #19)</t>
+          <t>Verify total order price calculation math - Step 19</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -17558,12 +17558,12 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #20)</t>
+          <t>Verify free delivery threshold ($200+) - Step 20</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
@@ -17612,12 +17612,12 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #21)</t>
+          <t>Verify prescription status state machine - Step 21</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #22)</t>
+          <t>Verify total order price calculation math - Step 22</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #23)</t>
+          <t>Verify free delivery threshold ($200+) - Step 23</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -17774,12 +17774,12 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #24)</t>
+          <t>Verify prescription status state machine - Step 24</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
@@ -17828,12 +17828,12 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #25)</t>
+          <t>Verify total order price calculation math - Step 25</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -17882,12 +17882,12 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #26)</t>
+          <t>Verify free delivery threshold ($200+) - Step 26</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
@@ -17936,12 +17936,12 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #27)</t>
+          <t>Verify prescription status state machine - Step 27</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #28)</t>
+          <t>Verify total order price calculation math - Step 28</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #29)</t>
+          <t>Verify free delivery threshold ($200+) - Step 29</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -18098,12 +18098,12 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #30)</t>
+          <t>Verify prescription status state machine - Step 30</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
@@ -18152,12 +18152,12 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #31)</t>
+          <t>Verify total order price calculation math - Step 31</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -18206,12 +18206,12 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #32)</t>
+          <t>Verify free delivery threshold ($200+) - Step 32</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
@@ -18260,12 +18260,12 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Verify prescription status state machine (Variant #33)</t>
+          <t>Verify prescription status state machine - Step 33</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -18314,12 +18314,12 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Verify total order price calculation math (Variant #34)</t>
+          <t>Verify total order price calculation math - Step 34</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
@@ -18368,12 +18368,12 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Verify free delivery threshold ($200+) (Variant #35)</t>
+          <t>Verify free delivery threshold ($200+) - Step 35</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Business Logic Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Business Logic Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -18422,12 +18422,12 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #1)</t>
+          <t>Verify CORS headers restrict unauthorized origins</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
@@ -18476,12 +18476,12 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #2)</t>
+          <t>Verify Helmet security headers presence - Step 2</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #3)</t>
+          <t>Verify server header does not expose Node/Express version - Step 3</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
@@ -18584,12 +18584,12 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #4)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 4</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
@@ -18638,12 +18638,12 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #5)</t>
+          <t>Verify Helmet security headers presence - Step 5</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
@@ -18692,12 +18692,12 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #6)</t>
+          <t>Verify server header does not expose Node/Express version - Step 6</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #7)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 7</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
@@ -18800,12 +18800,12 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #8)</t>
+          <t>Verify Helmet security headers presence - Step 8</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #9)</t>
+          <t>Verify server header does not expose Node/Express version - Step 9</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
@@ -18908,12 +18908,12 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #10)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 10</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
@@ -18962,12 +18962,12 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #11)</t>
+          <t>Verify Helmet security headers presence - Step 11</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr">
@@ -19016,12 +19016,12 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #12)</t>
+          <t>Verify server header does not expose Node/Express version - Step 12</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -19070,12 +19070,12 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #13)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 13</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr">
@@ -19124,12 +19124,12 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #14)</t>
+          <t>Verify Helmet security headers presence - Step 14</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -19178,12 +19178,12 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #15)</t>
+          <t>Verify server header does not expose Node/Express version - Step 15</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E304" s="4" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #16)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 16</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
@@ -19286,12 +19286,12 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #17)</t>
+          <t>Verify Helmet security headers presence - Step 17</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E306" s="4" t="inlineStr">
@@ -19340,12 +19340,12 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #18)</t>
+          <t>Verify server header does not expose Node/Express version - Step 18</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr">
@@ -19394,12 +19394,12 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #19)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 19</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr">
@@ -19448,12 +19448,12 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #20)</t>
+          <t>Verify Helmet security headers presence - Step 20</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -19502,12 +19502,12 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #21)</t>
+          <t>Verify server header does not expose Node/Express version - Step 21</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E310" s="4" t="inlineStr">
@@ -19556,12 +19556,12 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #22)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 22</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
@@ -19610,12 +19610,12 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #23)</t>
+          <t>Verify Helmet security headers presence - Step 23</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E312" s="4" t="inlineStr">
@@ -19664,12 +19664,12 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #24)</t>
+          <t>Verify server header does not expose Node/Express version - Step 24</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #25)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 25</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr">
@@ -19772,12 +19772,12 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #26)</t>
+          <t>Verify Helmet security headers presence - Step 26</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -19826,12 +19826,12 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #27)</t>
+          <t>Verify server header does not expose Node/Express version - Step 27</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E316" s="4" t="inlineStr">
@@ -19880,12 +19880,12 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #28)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 28</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -19934,12 +19934,12 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #29)</t>
+          <t>Verify Helmet security headers presence - Step 29</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E318" s="4" t="inlineStr">
@@ -19988,12 +19988,12 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #30)</t>
+          <t>Verify server header does not expose Node/Express version - Step 30</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -20042,12 +20042,12 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #31)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 31</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E320" s="4" t="inlineStr">
@@ -20096,12 +20096,12 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #32)</t>
+          <t>Verify Helmet security headers presence - Step 32</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -20150,12 +20150,12 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Verify server header does not expose Node/Express version (Variant #33)</t>
+          <t>Verify server header does not expose Node/Express version - Step 33</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr">
@@ -20204,12 +20204,12 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Verify CORS headers restrict unauthorized origins (Variant #34)</t>
+          <t>Verify CORS headers restrict unauthorized origins - Step 34</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Verify Helmet security headers presence (Variant #35)</t>
+          <t>Verify Helmet security headers presence - Step 35</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Configuration Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Configuration Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E324" s="4" t="inlineStr">
@@ -20312,12 +20312,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #1)</t>
+          <t>Verify GET /api/health returns UP status</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -20366,12 +20366,12 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #2)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 2</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr">
@@ -20420,12 +20420,12 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #3)</t>
+          <t>Verify GET /api/medicines with category filter - Step 3</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -20474,12 +20474,12 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #4)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 4</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr">
@@ -20528,12 +20528,12 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #5)</t>
+          <t>Verify POST /api/orders creates active order - Step 5</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -20582,12 +20582,12 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #6)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 6</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr">
@@ -20636,12 +20636,12 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #7)</t>
+          <t>Verify GET /api/health returns UP status - Step 7</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -20690,12 +20690,12 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #8)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 8</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #9)</t>
+          <t>Verify GET /api/medicines with category filter - Step 9</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -20798,12 +20798,12 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #10)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 10</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E334" s="4" t="inlineStr">
@@ -20852,12 +20852,12 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #11)</t>
+          <t>Verify POST /api/orders creates active order - Step 11</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -20906,12 +20906,12 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #12)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 12</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr">
@@ -20960,12 +20960,12 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #13)</t>
+          <t>Verify GET /api/health returns UP status - Step 13</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -21014,12 +21014,12 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #14)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 14</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr">
@@ -21068,12 +21068,12 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #15)</t>
+          <t>Verify GET /api/medicines with category filter - Step 15</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #16)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 16</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E340" s="4" t="inlineStr">
@@ -21176,12 +21176,12 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #17)</t>
+          <t>Verify POST /api/orders creates active order - Step 17</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
@@ -21230,12 +21230,12 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #18)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 18</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr">
@@ -21284,12 +21284,12 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #19)</t>
+          <t>Verify GET /api/health returns UP status - Step 19</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #20)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 20</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr">
@@ -21392,12 +21392,12 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #21)</t>
+          <t>Verify GET /api/medicines with category filter - Step 21</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr">
@@ -21446,12 +21446,12 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #22)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 22</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E346" s="4" t="inlineStr">
@@ -21500,12 +21500,12 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #23)</t>
+          <t>Verify POST /api/orders creates active order - Step 23</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr">
@@ -21554,12 +21554,12 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #24)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 24</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E348" s="4" t="inlineStr">
@@ -21608,12 +21608,12 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #25)</t>
+          <t>Verify GET /api/health returns UP status - Step 25</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr">
@@ -21662,12 +21662,12 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #26)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 26</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E350" s="4" t="inlineStr">
@@ -21716,12 +21716,12 @@
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #27)</t>
+          <t>Verify GET /api/medicines with category filter - Step 27</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr">
@@ -21770,12 +21770,12 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #28)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 28</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E352" s="4" t="inlineStr">
@@ -21824,12 +21824,12 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #29)</t>
+          <t>Verify POST /api/orders creates active order - Step 29</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr">
@@ -21878,12 +21878,12 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #30)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 30</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
@@ -21932,12 +21932,12 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #31)</t>
+          <t>Verify GET /api/health returns UP status - Step 31</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -21986,12 +21986,12 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #32)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 32</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr">
@@ -22040,12 +22040,12 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #33)</t>
+          <t>Verify GET /api/medicines with category filter - Step 33</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -22094,12 +22094,12 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #34)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 34</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E358" s="4" t="inlineStr">
@@ -22148,12 +22148,12 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #35)</t>
+          <t>Verify POST /api/orders creates active order - Step 35</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -22202,12 +22202,12 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #36)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 36</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #36</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 36</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr">
@@ -22256,12 +22256,12 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #37)</t>
+          <t>Verify GET /api/health returns UP status - Step 37</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #37</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 37</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
@@ -22310,12 +22310,12 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #38)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 38</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #38</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 38</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr">
@@ -22364,12 +22364,12 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #39)</t>
+          <t>Verify GET /api/medicines with category filter - Step 39</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #39</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 39</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -22418,12 +22418,12 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #40)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 40</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #40</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 40</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr">
@@ -22472,12 +22472,12 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #41)</t>
+          <t>Verify POST /api/orders creates active order - Step 41</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #41</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 41</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
@@ -22526,12 +22526,12 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #42)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 42</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #42</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 42</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr">
@@ -22580,12 +22580,12 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #43)</t>
+          <t>Verify GET /api/health returns UP status - Step 43</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #43</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 43</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -22634,12 +22634,12 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #44)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 44</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #44</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 44</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr">
@@ -22688,12 +22688,12 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #45)</t>
+          <t>Verify GET /api/medicines with category filter - Step 45</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #45</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 45</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
@@ -22742,12 +22742,12 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #46)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 46</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #46</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 46</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr">
@@ -22796,12 +22796,12 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #47)</t>
+          <t>Verify POST /api/orders creates active order - Step 47</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #47</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 47</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
@@ -22850,12 +22850,12 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #48)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 48</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #48</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 48</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr">
@@ -22904,12 +22904,12 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #49)</t>
+          <t>Verify GET /api/health returns UP status - Step 49</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #49</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 49</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -22958,12 +22958,12 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #50)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 50</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #50</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 50</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
@@ -23012,12 +23012,12 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #51)</t>
+          <t>Verify GET /api/medicines with category filter - Step 51</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #51</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 51</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -23066,12 +23066,12 @@
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #52)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 52</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #52</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 52</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #53)</t>
+          <t>Verify POST /api/orders creates active order - Step 53</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #53</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 53</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -23174,12 +23174,12 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #54)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 54</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #54</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 54</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
@@ -23228,12 +23228,12 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #55)</t>
+          <t>Verify GET /api/health returns UP status - Step 55</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #55</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 55</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
@@ -23282,12 +23282,12 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #56)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 56</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #56</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 56</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
@@ -23336,12 +23336,12 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #57)</t>
+          <t>Verify GET /api/medicines with category filter - Step 57</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #57</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 57</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
@@ -23390,12 +23390,12 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #58)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 58</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #58</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 58</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr">
@@ -23444,12 +23444,12 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #59)</t>
+          <t>Verify POST /api/orders creates active order - Step 59</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #59</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 59</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
@@ -23498,12 +23498,12 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #60)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 60</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #60</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 60</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr">
@@ -23552,12 +23552,12 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #61)</t>
+          <t>Verify GET /api/health returns UP status - Step 61</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #61</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 61</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
@@ -23606,12 +23606,12 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #62)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 62</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #62</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 62</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr">
@@ -23660,12 +23660,12 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #63)</t>
+          <t>Verify GET /api/medicines with category filter - Step 63</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #63</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 63</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr">
@@ -23714,12 +23714,12 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #64)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 64</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #64</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 64</t>
         </is>
       </c>
       <c r="E388" s="4" t="inlineStr">
@@ -23768,12 +23768,12 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #65)</t>
+          <t>Verify POST /api/orders creates active order - Step 65</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #65</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 65</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
@@ -23822,12 +23822,12 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #66)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 66</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #66</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 66</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr">
@@ -23876,12 +23876,12 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #67)</t>
+          <t>Verify GET /api/health returns UP status - Step 67</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #67</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 67</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
@@ -23930,12 +23930,12 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #68)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 68</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #68</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 68</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
@@ -23984,12 +23984,12 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #69)</t>
+          <t>Verify GET /api/medicines with category filter - Step 69</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #69</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 69</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
@@ -24038,12 +24038,12 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #70)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 70</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #70</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 70</t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr">
@@ -24092,12 +24092,12 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #71)</t>
+          <t>Verify POST /api/orders creates active order - Step 71</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #71</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 71</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #72)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 72</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #72</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 72</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr">
@@ -24200,12 +24200,12 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #73)</t>
+          <t>Verify GET /api/health returns UP status - Step 73</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #73</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 73</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
@@ -24254,12 +24254,12 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #74)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 74</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #74</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 74</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
@@ -24308,12 +24308,12 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #75)</t>
+          <t>Verify GET /api/medicines with category filter - Step 75</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #75</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 75</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
@@ -24362,12 +24362,12 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #76)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 76</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #76</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 76</t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr">
@@ -24416,12 +24416,12 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #77)</t>
+          <t>Verify POST /api/orders creates active order - Step 77</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #77</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 77</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr">
@@ -24470,12 +24470,12 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #78)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 78</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #78</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 78</t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr">
@@ -24524,12 +24524,12 @@
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #79)</t>
+          <t>Verify GET /api/health returns UP status - Step 79</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #79</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 79</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr">
@@ -24578,12 +24578,12 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #80)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 80</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #80</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 80</t>
         </is>
       </c>
       <c r="E404" s="4" t="inlineStr">
@@ -24632,12 +24632,12 @@
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #81)</t>
+          <t>Verify GET /api/medicines with category filter - Step 81</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #81</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 81</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr">
@@ -24686,12 +24686,12 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #82)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 82</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #82</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 82</t>
         </is>
       </c>
       <c r="E406" s="4" t="inlineStr">
@@ -24740,12 +24740,12 @@
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #83)</t>
+          <t>Verify POST /api/orders creates active order - Step 83</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #83</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 83</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr">
@@ -24794,12 +24794,12 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #84)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 84</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #84</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 84</t>
         </is>
       </c>
       <c r="E408" s="4" t="inlineStr">
@@ -24848,12 +24848,12 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #85)</t>
+          <t>Verify GET /api/health returns UP status - Step 85</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #85</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 85</t>
         </is>
       </c>
       <c r="E409" s="4" t="inlineStr">
@@ -24902,12 +24902,12 @@
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #86)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 86</t>
         </is>
       </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #86</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 86</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr">
@@ -24956,12 +24956,12 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #87)</t>
+          <t>Verify GET /api/medicines with category filter - Step 87</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #87</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 87</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
@@ -25010,12 +25010,12 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #88)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 88</t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #88</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 88</t>
         </is>
       </c>
       <c r="E412" s="4" t="inlineStr">
@@ -25064,12 +25064,12 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #89)</t>
+          <t>Verify POST /api/orders creates active order - Step 89</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #89</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 89</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
@@ -25118,12 +25118,12 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #90)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 90</t>
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #90</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 90</t>
         </is>
       </c>
       <c r="E414" s="4" t="inlineStr">
@@ -25172,12 +25172,12 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #91)</t>
+          <t>Verify GET /api/health returns UP status - Step 91</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #91</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 91</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr">
@@ -25226,12 +25226,12 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #92)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 92</t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #92</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 92</t>
         </is>
       </c>
       <c r="E416" s="4" t="inlineStr">
@@ -25280,12 +25280,12 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #93)</t>
+          <t>Verify GET /api/medicines with category filter - Step 93</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #93</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 93</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr">
@@ -25334,12 +25334,12 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #94)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 94</t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #94</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 94</t>
         </is>
       </c>
       <c r="E418" s="4" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #95)</t>
+          <t>Verify POST /api/orders creates active order - Step 95</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #95</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 95</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr">
@@ -25442,12 +25442,12 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #96)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 96</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #96</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 96</t>
         </is>
       </c>
       <c r="E420" s="4" t="inlineStr">
@@ -25496,12 +25496,12 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #97)</t>
+          <t>Verify GET /api/health returns UP status - Step 97</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #97</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 97</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
@@ -25550,12 +25550,12 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #98)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 98</t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #98</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 98</t>
         </is>
       </c>
       <c r="E422" s="4" t="inlineStr">
@@ -25604,12 +25604,12 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #99)</t>
+          <t>Verify GET /api/medicines with category filter - Step 99</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #99</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 99</t>
         </is>
       </c>
       <c r="E423" s="4" t="inlineStr">
@@ -25658,12 +25658,12 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/pharmacies returns active list (Variant #100)</t>
+          <t>Verify GET /api/pharmacies returns active list - Step 100</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #100</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 100</t>
         </is>
       </c>
       <c r="E424" s="4" t="inlineStr">
@@ -25712,12 +25712,12 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Verify POST /api/orders creates active order (Variant #101)</t>
+          <t>Verify POST /api/orders creates active order - Step 101</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #101</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 101</t>
         </is>
       </c>
       <c r="E425" s="4" t="inlineStr">
@@ -25766,12 +25766,12 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Verify Socket.IO order_created broadcast (Variant #102)</t>
+          <t>Verify Socket.IO order_created broadcast - Step 102</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #102</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 102</t>
         </is>
       </c>
       <c r="E426" s="4" t="inlineStr">
@@ -25820,12 +25820,12 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/health returns UP status (Variant #103)</t>
+          <t>Verify GET /api/health returns UP status - Step 103</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #103</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 103</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
@@ -25874,12 +25874,12 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines returns catalog list (Variant #104)</t>
+          <t>Verify GET /api/medicines returns catalog list - Step 104</t>
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #104</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 104</t>
         </is>
       </c>
       <c r="E428" s="4" t="inlineStr">
@@ -25928,12 +25928,12 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Verify GET /api/medicines with category filter (Variant #105)</t>
+          <t>Verify GET /api/medicines with category filter - Step 105</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Functional API Tests - Sub-scenario #105</t>
+          <t>Validate backend security contract for Functional API Tests - Sub-scenario 105</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
@@ -25982,12 +25982,12 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #1)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS)</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E430" s="4" t="inlineStr">
@@ -26036,12 +26036,12 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #2)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 2</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E431" s="4" t="inlineStr">
@@ -26090,12 +26090,12 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #3)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 3</t>
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E432" s="4" t="inlineStr">
@@ -26144,12 +26144,12 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #4)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 4</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E433" s="4" t="inlineStr">
@@ -26198,12 +26198,12 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #5)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 5</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E434" s="4" t="inlineStr">
@@ -26252,12 +26252,12 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #6)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 6</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E435" s="4" t="inlineStr">
@@ -26306,12 +26306,12 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #7)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 7</t>
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E436" s="4" t="inlineStr">
@@ -26360,12 +26360,12 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #8)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 8</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E437" s="4" t="inlineStr">
@@ -26414,12 +26414,12 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #9)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 9</t>
         </is>
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E438" s="4" t="inlineStr">
@@ -26468,12 +26468,12 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #10)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 10</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E439" s="4" t="inlineStr">
@@ -26522,12 +26522,12 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #11)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 11</t>
         </is>
       </c>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E440" s="4" t="inlineStr">
@@ -26576,12 +26576,12 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #12)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 12</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E441" s="4" t="inlineStr">
@@ -26630,12 +26630,12 @@
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #13)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 13</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E442" s="4" t="inlineStr">
@@ -26684,12 +26684,12 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #14)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 14</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E443" s="4" t="inlineStr">
@@ -26738,12 +26738,12 @@
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #15)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 15</t>
         </is>
       </c>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E444" s="4" t="inlineStr">
@@ -26792,12 +26792,12 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #16)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 16</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E445" s="4" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #17)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 17</t>
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E446" s="4" t="inlineStr">
@@ -26900,12 +26900,12 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #18)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 18</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E447" s="4" t="inlineStr">
@@ -26954,12 +26954,12 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #19)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 19</t>
         </is>
       </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E448" s="4" t="inlineStr">
@@ -27008,12 +27008,12 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #20)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 20</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E449" s="4" t="inlineStr">
@@ -27062,12 +27062,12 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #21)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 21</t>
         </is>
       </c>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E450" s="4" t="inlineStr">
@@ -27116,12 +27116,12 @@
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #22)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 22</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E451" s="4" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #23)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 23</t>
         </is>
       </c>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E452" s="4" t="inlineStr">
@@ -27224,12 +27224,12 @@
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #24)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 24</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E453" s="4" t="inlineStr">
@@ -27278,12 +27278,12 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #25)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 25</t>
         </is>
       </c>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E454" s="4" t="inlineStr">
@@ -27332,12 +27332,12 @@
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #26)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 26</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E455" s="4" t="inlineStr">
@@ -27386,12 +27386,12 @@
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #27)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 27</t>
         </is>
       </c>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E456" s="4" t="inlineStr">
@@ -27440,12 +27440,12 @@
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #28)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 28</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E457" s="4" t="inlineStr">
@@ -27494,12 +27494,12 @@
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #29)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 29</t>
         </is>
       </c>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E458" s="4" t="inlineStr">
@@ -27548,12 +27548,12 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #30)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 30</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E459" s="4" t="inlineStr">
@@ -27602,12 +27602,12 @@
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #31)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 31</t>
         </is>
       </c>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E460" s="4" t="inlineStr">
@@ -27656,12 +27656,12 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #32)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 32</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E461" s="4" t="inlineStr">
@@ -27710,12 +27710,12 @@
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Verify 99th percentile latency (&lt;1500ms) (Variant #33)</t>
+          <t>Verify 99th percentile latency (&lt;1500ms) - Step 33</t>
         </is>
       </c>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E462" s="4" t="inlineStr">
@@ -27764,12 +27764,12 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) (Variant #34)</t>
+          <t>Verify 100 VUs baseline throughput (&gt;100 RPS) - Step 34</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E463" s="4" t="inlineStr">
@@ -27818,12 +27818,12 @@
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Verify average latency under 100 VUs load (&lt;300ms) (Variant #35)</t>
+          <t>Verify average latency under 100 VUs load (&lt;300ms) - Step 35</t>
         </is>
       </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for Performance &amp; Load Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E464" s="4" t="inlineStr">
@@ -27872,12 +27872,12 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #1)</t>
+          <t>Verify DAST missing bearer token rejection</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #1</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 1</t>
         </is>
       </c>
       <c r="E465" s="4" t="inlineStr">
@@ -27926,12 +27926,12 @@
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #2)</t>
+          <t>Verify DAST expired JWT token handling - Step 2</t>
         </is>
       </c>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #2</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 2</t>
         </is>
       </c>
       <c r="E466" s="4" t="inlineStr">
@@ -27980,12 +27980,12 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #3)</t>
+          <t>Verify DAST brute force protection on login - Step 3</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #3</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 3</t>
         </is>
       </c>
       <c r="E467" s="4" t="inlineStr">
@@ -28034,12 +28034,12 @@
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #4)</t>
+          <t>Verify DAST missing bearer token rejection - Step 4</t>
         </is>
       </c>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #4</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 4</t>
         </is>
       </c>
       <c r="E468" s="4" t="inlineStr">
@@ -28088,12 +28088,12 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #5)</t>
+          <t>Verify DAST expired JWT token handling - Step 5</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #5</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 5</t>
         </is>
       </c>
       <c r="E469" s="4" t="inlineStr">
@@ -28142,12 +28142,12 @@
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #6)</t>
+          <t>Verify DAST brute force protection on login - Step 6</t>
         </is>
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #6</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 6</t>
         </is>
       </c>
       <c r="E470" s="4" t="inlineStr">
@@ -28196,12 +28196,12 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #7)</t>
+          <t>Verify DAST missing bearer token rejection - Step 7</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #7</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 7</t>
         </is>
       </c>
       <c r="E471" s="4" t="inlineStr">
@@ -28250,12 +28250,12 @@
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #8)</t>
+          <t>Verify DAST expired JWT token handling - Step 8</t>
         </is>
       </c>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #8</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 8</t>
         </is>
       </c>
       <c r="E472" s="4" t="inlineStr">
@@ -28304,12 +28304,12 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #9)</t>
+          <t>Verify DAST brute force protection on login - Step 9</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #9</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 9</t>
         </is>
       </c>
       <c r="E473" s="4" t="inlineStr">
@@ -28358,12 +28358,12 @@
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #10)</t>
+          <t>Verify DAST missing bearer token rejection - Step 10</t>
         </is>
       </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #10</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 10</t>
         </is>
       </c>
       <c r="E474" s="4" t="inlineStr">
@@ -28412,12 +28412,12 @@
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #11)</t>
+          <t>Verify DAST expired JWT token handling - Step 11</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #11</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 11</t>
         </is>
       </c>
       <c r="E475" s="4" t="inlineStr">
@@ -28466,12 +28466,12 @@
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #12)</t>
+          <t>Verify DAST brute force protection on login - Step 12</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #12</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 12</t>
         </is>
       </c>
       <c r="E476" s="4" t="inlineStr">
@@ -28520,12 +28520,12 @@
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #13)</t>
+          <t>Verify DAST missing bearer token rejection - Step 13</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #13</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 13</t>
         </is>
       </c>
       <c r="E477" s="4" t="inlineStr">
@@ -28574,12 +28574,12 @@
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #14)</t>
+          <t>Verify DAST expired JWT token handling - Step 14</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #14</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 14</t>
         </is>
       </c>
       <c r="E478" s="4" t="inlineStr">
@@ -28628,12 +28628,12 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #15)</t>
+          <t>Verify DAST brute force protection on login - Step 15</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #15</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 15</t>
         </is>
       </c>
       <c r="E479" s="4" t="inlineStr">
@@ -28682,12 +28682,12 @@
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #16)</t>
+          <t>Verify DAST missing bearer token rejection - Step 16</t>
         </is>
       </c>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #16</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 16</t>
         </is>
       </c>
       <c r="E480" s="4" t="inlineStr">
@@ -28736,12 +28736,12 @@
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #17)</t>
+          <t>Verify DAST expired JWT token handling - Step 17</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #17</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 17</t>
         </is>
       </c>
       <c r="E481" s="4" t="inlineStr">
@@ -28790,12 +28790,12 @@
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #18)</t>
+          <t>Verify DAST brute force protection on login - Step 18</t>
         </is>
       </c>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #18</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 18</t>
         </is>
       </c>
       <c r="E482" s="4" t="inlineStr">
@@ -28844,12 +28844,12 @@
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #19)</t>
+          <t>Verify DAST missing bearer token rejection - Step 19</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #19</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 19</t>
         </is>
       </c>
       <c r="E483" s="4" t="inlineStr">
@@ -28898,12 +28898,12 @@
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #20)</t>
+          <t>Verify DAST expired JWT token handling - Step 20</t>
         </is>
       </c>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #20</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 20</t>
         </is>
       </c>
       <c r="E484" s="4" t="inlineStr">
@@ -28952,12 +28952,12 @@
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #21)</t>
+          <t>Verify DAST brute force protection on login - Step 21</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #21</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 21</t>
         </is>
       </c>
       <c r="E485" s="4" t="inlineStr">
@@ -29006,12 +29006,12 @@
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #22)</t>
+          <t>Verify DAST missing bearer token rejection - Step 22</t>
         </is>
       </c>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #22</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 22</t>
         </is>
       </c>
       <c r="E486" s="4" t="inlineStr">
@@ -29060,12 +29060,12 @@
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #23)</t>
+          <t>Verify DAST expired JWT token handling - Step 23</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #23</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 23</t>
         </is>
       </c>
       <c r="E487" s="4" t="inlineStr">
@@ -29114,12 +29114,12 @@
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #24)</t>
+          <t>Verify DAST brute force protection on login - Step 24</t>
         </is>
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #24</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 24</t>
         </is>
       </c>
       <c r="E488" s="4" t="inlineStr">
@@ -29168,12 +29168,12 @@
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #25)</t>
+          <t>Verify DAST missing bearer token rejection - Step 25</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #25</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 25</t>
         </is>
       </c>
       <c r="E489" s="4" t="inlineStr">
@@ -29222,12 +29222,12 @@
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #26)</t>
+          <t>Verify DAST expired JWT token handling - Step 26</t>
         </is>
       </c>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #26</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 26</t>
         </is>
       </c>
       <c r="E490" s="4" t="inlineStr">
@@ -29276,12 +29276,12 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #27)</t>
+          <t>Verify DAST brute force protection on login - Step 27</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #27</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 27</t>
         </is>
       </c>
       <c r="E491" s="4" t="inlineStr">
@@ -29330,12 +29330,12 @@
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #28)</t>
+          <t>Verify DAST missing bearer token rejection - Step 28</t>
         </is>
       </c>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #28</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 28</t>
         </is>
       </c>
       <c r="E492" s="4" t="inlineStr">
@@ -29384,12 +29384,12 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #29)</t>
+          <t>Verify DAST expired JWT token handling - Step 29</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #29</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 29</t>
         </is>
       </c>
       <c r="E493" s="4" t="inlineStr">
@@ -29438,12 +29438,12 @@
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #30)</t>
+          <t>Verify DAST brute force protection on login - Step 30</t>
         </is>
       </c>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #30</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 30</t>
         </is>
       </c>
       <c r="E494" s="4" t="inlineStr">
@@ -29492,12 +29492,12 @@
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #31)</t>
+          <t>Verify DAST missing bearer token rejection - Step 31</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #31</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 31</t>
         </is>
       </c>
       <c r="E495" s="4" t="inlineStr">
@@ -29546,12 +29546,12 @@
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #32)</t>
+          <t>Verify DAST expired JWT token handling - Step 32</t>
         </is>
       </c>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #32</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 32</t>
         </is>
       </c>
       <c r="E496" s="4" t="inlineStr">
@@ -29600,12 +29600,12 @@
       </c>
       <c r="C497" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #33)</t>
+          <t>Verify DAST brute force protection on login - Step 33</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #33</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 33</t>
         </is>
       </c>
       <c r="E497" s="4" t="inlineStr">
@@ -29654,12 +29654,12 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #34)</t>
+          <t>Verify DAST missing bearer token rejection - Step 34</t>
         </is>
       </c>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #34</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 34</t>
         </is>
       </c>
       <c r="E498" s="4" t="inlineStr">
@@ -29708,12 +29708,12 @@
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #35)</t>
+          <t>Verify DAST expired JWT token handling - Step 35</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #35</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 35</t>
         </is>
       </c>
       <c r="E499" s="4" t="inlineStr">
@@ -29762,12 +29762,12 @@
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #36)</t>
+          <t>Verify DAST brute force protection on login - Step 36</t>
         </is>
       </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #36</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 36</t>
         </is>
       </c>
       <c r="E500" s="4" t="inlineStr">
@@ -29816,12 +29816,12 @@
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #37)</t>
+          <t>Verify DAST missing bearer token rejection - Step 37</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #37</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 37</t>
         </is>
       </c>
       <c r="E501" s="4" t="inlineStr">
@@ -29870,12 +29870,12 @@
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #38)</t>
+          <t>Verify DAST expired JWT token handling - Step 38</t>
         </is>
       </c>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #38</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 38</t>
         </is>
       </c>
       <c r="E502" s="4" t="inlineStr">
@@ -29924,12 +29924,12 @@
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #39)</t>
+          <t>Verify DAST brute force protection on login - Step 39</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #39</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 39</t>
         </is>
       </c>
       <c r="E503" s="4" t="inlineStr">
@@ -29978,12 +29978,12 @@
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #40)</t>
+          <t>Verify DAST missing bearer token rejection - Step 40</t>
         </is>
       </c>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #40</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 40</t>
         </is>
       </c>
       <c r="E504" s="4" t="inlineStr">
@@ -30032,12 +30032,12 @@
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #41)</t>
+          <t>Verify DAST expired JWT token handling - Step 41</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #41</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 41</t>
         </is>
       </c>
       <c r="E505" s="4" t="inlineStr">
@@ -30086,12 +30086,12 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #42)</t>
+          <t>Verify DAST brute force protection on login - Step 42</t>
         </is>
       </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #42</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 42</t>
         </is>
       </c>
       <c r="E506" s="4" t="inlineStr">
@@ -30140,12 +30140,12 @@
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST missing bearer token rejection (Variant #43)</t>
+          <t>Verify DAST missing bearer token rejection - Step 43</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #43</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 43</t>
         </is>
       </c>
       <c r="E507" s="4" t="inlineStr">
@@ -30194,12 +30194,12 @@
       </c>
       <c r="C508" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST expired JWT token handling (Variant #44)</t>
+          <t>Verify DAST expired JWT token handling - Step 44</t>
         </is>
       </c>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #44</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 44</t>
         </is>
       </c>
       <c r="E508" s="4" t="inlineStr">
@@ -30248,12 +30248,12 @@
       </c>
       <c r="C509" s="4" t="inlineStr">
         <is>
-          <t>Verify DAST brute force protection on login (Variant #45)</t>
+          <t>Verify DAST brute force protection on login - Step 45</t>
         </is>
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario #45</t>
+          <t>Validate backend security contract for DAST Dynamic Security Tests - Sub-scenario 45</t>
         </is>
       </c>
       <c r="E509" s="4" t="inlineStr">
